--- a/data/trans_dic/IP04D$colectiva-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,59</t>
+          <t>0,0; 7,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,72</t>
+          <t>0,0; 8,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,49</t>
+          <t>0,76; 6,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,16</t>
+          <t>0,74; 4,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,36</t>
+          <t>0,36; 4,2</t>
         </is>
       </c>
     </row>
@@ -785,22 +788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,2</t>
+          <t>1,73; 4,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,97</t>
+          <t>1,35; 3,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 7,4</t>
+          <t>3,67; 7,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,74</t>
+          <t>1,3; 3,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -810,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,19</t>
+          <t>3,8; 7,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,57</t>
+          <t>1,78; 3,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,78</t>
+          <t>1,32; 2,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,56</t>
+          <t>4,27; 6,68</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 10,04</t>
+          <t>3,72; 9,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 11,53</t>
+          <t>4,65; 11,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,68; 22,7</t>
+          <t>12,43; 23,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,96</t>
+          <t>2,45; 8,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 14,65</t>
+          <t>6,86; 14,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,53; 18,56</t>
+          <t>9,66; 18,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 8,08</t>
+          <t>3,79; 7,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,64</t>
+          <t>6,38; 11,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,92; 19,0</t>
+          <t>12,17; 18,87</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,79</t>
+          <t>2,54; 4,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,7</t>
+          <t>2,48; 4,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,13; 9,98</t>
+          <t>6,29; 9,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,03</t>
+          <t>1,91; 4,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,84</t>
+          <t>2,62; 4,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,64</t>
+          <t>5,56; 8,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,05</t>
+          <t>2,45; 3,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,33</t>
+          <t>2,79; 4,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,24; 8,59</t>
+          <t>6,2; 8,65</t>
         </is>
       </c>
     </row>
@@ -1069,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3322</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1758</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4440</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4303</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4645</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>659; 5580</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2193</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1314; 7301</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3823</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>416; 4897</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12727</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10866</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24914</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11094</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7378</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27470</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>23821</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>18245</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>52384</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7782; 19240</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6362; 17330</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16919; 33144</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6415; 17955</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3705; 13278</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19622; 37146</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>16817; 33716</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>12660; 26637</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>41716; 65211</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10810</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12657</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25879</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7821</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>18830</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24866</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>18631</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>31486</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>50746</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>6198; 16625</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7940; 19464</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18458; 35582</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4217; 14073</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12704; 26777</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>17619; 33920</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12833; 26556</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>22705; 40869</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>40273; 62464</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>24802</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24276</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52125</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26208</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52763</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>45774</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>50484</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>104888</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>17982; 34398</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17392; 33867</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>41768; 65258</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>14368; 30790</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>19382; 35710</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>42303; 65963</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>35766; 57105</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>40111; 64109</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>88361; 123121</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$colectiva-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Estudios-trans_dic.xlsx
@@ -678,22 +678,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,32</t>
+          <t>0,0; 6,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,5</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,47</t>
+          <t>0,76; 6,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,09</t>
+          <t>0,72; 3,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,2</t>
+          <t>0,38; 4,48</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,28</t>
+          <t>1,73; 4,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,68</t>
+          <t>1,32; 3,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,2</t>
+          <t>3,91; 7,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,64</t>
+          <t>1,28; 3,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,73</t>
+          <t>0,76; 2,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,2</t>
+          <t>3,82; 7,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,58</t>
+          <t>1,77; 3,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,78</t>
+          <t>1,25; 2,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 6,68</t>
+          <t>4,26; 6,87</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,97</t>
+          <t>3,73; 10,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 11,41</t>
+          <t>4,59; 11,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,43; 23,95</t>
+          <t>12,87; 23,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,17</t>
+          <t>2,56; 7,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 14,45</t>
+          <t>6,92; 14,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 18,6</t>
+          <t>9,76; 18,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,83</t>
+          <t>3,62; 7,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 11,48</t>
+          <t>6,66; 11,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,17; 18,87</t>
+          <t>12,19; 19,03</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,86</t>
+          <t>2,46; 4,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,84</t>
+          <t>2,57; 4,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 9,83</t>
+          <t>6,17; 9,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,1</t>
+          <t>1,9; 4,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,83</t>
+          <t>2,5; 4,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,68</t>
+          <t>5,4; 8,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,91</t>
+          <t>2,45; 4,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,45</t>
+          <t>2,78; 4,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,65</t>
+          <t>6,23; 8,69</t>
         </is>
       </c>
     </row>
@@ -1306,22 +1306,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4440</t>
+          <t>0; 4529</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4303</t>
+          <t>0; 3724</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4645</t>
+          <t>0; 4687</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>659; 5580</t>
+          <t>658; 5962</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1331,22 +1331,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2193</t>
+          <t>0; 2192</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1314; 7301</t>
+          <t>1293; 6992</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3823</t>
+          <t>0; 3740</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>416; 4897</t>
+          <t>448; 5232</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7782; 19240</t>
+          <t>7770; 19508</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6362; 17330</t>
+          <t>6213; 17049</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16919; 33144</t>
+          <t>18015; 34258</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6415; 17955</t>
+          <t>6303; 18533</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3705; 13278</t>
+          <t>3711; 13351</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19622; 37146</t>
+          <t>19708; 36891</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16817; 33716</t>
+          <t>16706; 33435</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12660; 26637</t>
+          <t>11997; 25971</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41716; 65211</t>
+          <t>41617; 67094</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6198; 16625</t>
+          <t>6221; 17419</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7940; 19464</t>
+          <t>7837; 18988</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18458; 35582</t>
+          <t>19114; 35082</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4217; 14073</t>
+          <t>4408; 13459</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12704; 26777</t>
+          <t>12830; 27288</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17619; 33920</t>
+          <t>17798; 34028</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12833; 26556</t>
+          <t>12258; 26485</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22705; 40869</t>
+          <t>23699; 42515</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40273; 62464</t>
+          <t>40340; 62989</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17982; 34398</t>
+          <t>17440; 32935</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17392; 33867</t>
+          <t>18023; 34452</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41768; 65258</t>
+          <t>40943; 64878</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14368; 30790</t>
+          <t>14248; 30058</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19382; 35710</t>
+          <t>18514; 35369</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42303; 65963</t>
+          <t>41076; 65804</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35766; 57105</t>
+          <t>35733; 58761</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40111; 64109</t>
+          <t>40100; 63666</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88361; 123121</t>
+          <t>88707; 123730</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$colectiva-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Estudios-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción colectiva en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,77; 6,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,92</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,54</t>
+          <t>0,0; 10,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,92</t>
+          <t>0,72; 4,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,48</t>
+          <t>0,34; 5,08</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>2,83%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,34</t>
+          <t>1,3; 3,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,62</t>
+          <t>0,76; 2,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,44</t>
+          <t>3,81; 7,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,76</t>
+          <t>1,72; 4,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,75</t>
+          <t>1,44; 3,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,15</t>
+          <t>4,15; 7,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,55</t>
+          <t>1,84; 3,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,71</t>
+          <t>1,31; 2,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 6,87</t>
+          <t>4,38; 6,71</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,48%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7,42%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,44</t>
+          <t>2,42; 7,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 11,13</t>
+          <t>7,16; 14,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,87; 23,62</t>
+          <t>9,18; 17,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,81</t>
+          <t>3,69; 10,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 14,73</t>
+          <t>4,61; 11,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 18,66</t>
+          <t>12,93; 23,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,81</t>
+          <t>3,84; 8,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,94</t>
+          <t>6,75; 11,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,19; 19,03</t>
+          <t>11,86; 18,94</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,65</t>
+          <t>1,95; 4,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,92</t>
+          <t>2,58; 4,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,77</t>
+          <t>5,36; 8,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,0</t>
+          <t>2,57; 4,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,78</t>
+          <t>2,46; 4,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,65</t>
+          <t>6,9; 10,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,03</t>
+          <t>2,49; 4,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,42</t>
+          <t>2,7; 4,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,69</t>
+          <t>6,45; 8,86</t>
         </is>
       </c>
     </row>
@@ -1099,20 +1099,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción colectiva en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1265</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>753</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1789</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4529</t>
+          <t>666; 5593</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3724</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4687</t>
+          <t>0; 1768</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>658; 5962</t>
+          <t>0; 3946</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3282</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2192</t>
+          <t>0; 5135</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1293; 6992</t>
+          <t>1279; 7421</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3740</t>
+          <t>0; 4567</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>448; 5232</t>
+          <t>356; 5257</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11094</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7378</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25156</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>12727</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>10866</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24914</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11094</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7378</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27470</t>
+          <t>25276</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>52384</t>
+          <t>50431</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7770; 19508</t>
+          <t>6399; 18436</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6213; 17049</t>
+          <t>3713; 13276</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18015; 34258</t>
+          <t>18089; 34275</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6303; 18533</t>
+          <t>7702; 18856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3711; 13351</t>
+          <t>6760; 18679</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19708; 36891</t>
+          <t>17945; 33618</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16706; 33435</t>
+          <t>17325; 33665</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11997; 25971</t>
+          <t>12516; 26555</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41617; 67094</t>
+          <t>39707; 60888</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>38</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7821</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18830</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22039</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>10810</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>12657</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25879</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7821</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>18830</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24866</t>
+          <t>26217</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50746</t>
+          <t>48255</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6221; 17419</t>
+          <t>4172; 13712</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7837; 18988</t>
+          <t>13263; 27142</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19114; 35082</t>
+          <t>15371; 29659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4408; 13459</t>
+          <t>6151; 16750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12830; 27288</t>
+          <t>7871; 19675</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17798; 34028</t>
+          <t>19253; 34325</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12258; 26485</t>
+          <t>13014; 27410</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23699; 42515</t>
+          <t>24010; 41435</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40340; 62989</t>
+          <t>37522; 59915</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26208</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>47551</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>24802</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>24276</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>52125</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20972</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>52924</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>104888</t>
+          <t>100475</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17440; 32935</t>
+          <t>14672; 30313</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18023; 34452</t>
+          <t>19093; 35833</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40943; 64878</t>
+          <t>37489; 59236</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14248; 30058</t>
+          <t>18213; 33912</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18514; 35369</t>
+          <t>17194; 32882</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41076; 65804</t>
+          <t>43343; 66072</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35733; 58761</t>
+          <t>36317; 59096</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40100; 63666</t>
+          <t>38814; 62323</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88707; 123730</t>
+          <t>85585; 117575</t>
         </is>
       </c>
     </row>
